--- a/output/pdf_financials_xlsx/LALI.xlsx
+++ b/output/pdf_financials_xlsx/LALI.xlsx
@@ -5650,19 +5650,19 @@
         <v>0</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>0.377</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="119">
@@ -10732,7 +10732,11 @@
           <t>Shares issued for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -12326,7 +12330,11 @@
           <t>Fair value of shares issued for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -12622,7 +12630,11 @@
           <t>Shares issued for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LALI.xlsx
+++ b/output/pdf_financials_xlsx/LALI.xlsx
@@ -888,16 +888,16 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.00045</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.011442</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.041699</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.058236</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1583,16 +1583,16 @@
         <v>-0.1923</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.609631</v>
+        <v>-0.610081</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.535282</v>
+        <v>-1.546724</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.775298</v>
+        <v>-0.816997</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.950337</v>
+        <v>-1.008573</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-2.487364</v>
@@ -1669,16 +1669,16 @@
         <v>-0.1923</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.609631</v>
+        <v>-0.610081</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.535282</v>
+        <v>-1.546724</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.775298</v>
+        <v>-0.816997</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.950337</v>
+        <v>-1.008573</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-2.487364</v>
@@ -1896,31 +1896,31 @@
         <v>0.012715</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.194282</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.164707</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.001987</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.301749</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.274111</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.155663</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.065139</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.006775</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.000891</v>
       </c>
     </row>
     <row r="35">
@@ -1982,31 +1982,31 @@
         <v>0.012715</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.194282</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.164707</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.001987</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.301749</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.274111</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.155663</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.075</v>
+        <v>0.140139</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.0375</v>
+        <v>0.044275</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.05</v>
+        <v>0.050891</v>
       </c>
     </row>
     <row r="37">
@@ -2498,31 +2498,31 @@
         <v>0.0052</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.443525</v>
+        <v>0.249243</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.477108</v>
+        <v>0.312401</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.348168</v>
+        <v>0.346181</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.404556</v>
+        <v>0.102807</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.39821</v>
+        <v>0.124099</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.277011</v>
+        <v>0.121348</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.258097</v>
+        <v>0.192958</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.019899</v>
+        <v>0.013124</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.016248</v>
+        <v>0.015357</v>
       </c>
     </row>
     <row r="49">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -16438,7 +16438,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -19590,7 +19590,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -21374,7 +21374,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -21898,7 +21898,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -22948,7 +22948,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">

--- a/output/pdf_financials_xlsx/LALI.xlsx
+++ b/output/pdf_financials_xlsx/LALI.xlsx
@@ -5337,7 +5337,7 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00168</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.288293</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>0</v>
@@ -5533,7 +5533,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.04866</v>
       </c>
     </row>
     <row r="116">
@@ -6358,7 +6358,7 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00168</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>-0.158892</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.6123769999999999</v>
+        <v>-0.614057</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-1.418657</v>
@@ -11492,7 +11492,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -11722,7 +11726,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E72" s="5" t="n">
         <v>0.24185</v>
       </c>
@@ -15166,7 +15174,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
